--- a/クロードセッションテスト/販売管理シート（excel版）.xlsx
+++ b/クロードセッションテスト/販売管理シート（excel版）.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\burok\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\burok\Desktop\クロードセッションテスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F49E200-3F60-4BDE-B68A-0DD180AFD49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386F79E4-A9CC-4AF1-B68A-55D132FF6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7ACCC311-AFC2-4939-B60A-3DEA33852035}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="139">
   <si>
     <t>Fedex 1.5kg</t>
   </si>
@@ -475,20 +475,48 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.ebay.com/itm/257541221721?_skw=Tamashii+Children&amp;epid=9040929430&amp;itmmeta=01M3PMXAY8T0MBEB09M1TN6B28&amp;hash=item3bf6a72d59:g:z3kAAeSwvtpqG5KA&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xCWrUzvE%2F6H6IP%2BMpO6h4R3KAfNT3ePjcw33Xlaj2ipyhZCl8eMGuOaTe6OjQKJHLyN0M5X%2F6sn7o5iV734ao9LquPJw9uHPX9p8dJvJTY91EBgCsq%2FsPo8PxamNySQEJO6uhqkWe6c%2FQCIfHg4EsuP%2F9yh7053Zb8L0LrOyY2qv%2Bq0U%2F7%2Fo8IQUcgboXrO6QnhE3lHWYMiCYg2jfxIhzcc4dTXH19stOnzbt920RvXPp0Ibb6dAsZxERs8OLYav4JiyMIrHndYy5722nOv7TTIG4HtdxunzxNEAcAH5Syeow%3D%3D%7Ctkp%3ABk9SR7Sv9dSdaA</t>
-  </si>
-  <si>
-    <t>https://www.ebay.com/itm/137557229227?_skw=Tamashii+Children&amp;itmmeta=01M3PMXAY93JCFX6KN6P87Y2BG&amp;hash=item20070cbeab:g:bXAAAeSwgPtqZ7V3&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xBtiicrm0UKxGxWVID%2Fw263CIAsJLC%2FS00bJyEQ2OriyxVz6Ya3MfKlKcZK0X%2ByomcAg3LpYCvmFuhU4PhDLyo6za8eR%2FVvzrIyRvhUTeQl9Z%2BuzUNt3Rlr7vkcYehPw8gchnJajOOZPuFCqprqiV1U2eRPeAI7LoXFsv%2BotNScixGJx8SpBqj%2F5J2QVNV1UWeSyU7JiO4pb7nAvK7ItIdHThLYxTT7%2BEZstD7mEATD%2BW6ypPc1MCDMt0lS89xuw6J%2B9PpwQP2SSUzYUslQTzgAm8bW7ENzhv14WJaGqz0WXQ%3D%3D%7Ctkp%3ABk9SR7av9dSdaA</t>
-  </si>
-  <si>
-    <t>https://www.ebay.com/itm/397497251172?_skw=Tamashii+Children&amp;itmmeta=01M3PMXAY7TPAXAVJT4D106BDT&amp;hash=item5c8caeb564:g:ChUAAeSwfaBpZ8VP&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xB2fq%2FTcC6aanFiph5rMQouRVmXFiKuT8u4%2FQ9%2F2VcMPnEEbaQMP5to0dkY3ZC2GjyMCCp36LPEuByrllb%2F0kf7HwsGuiDt85vECnKHNl3u2C%2BQWBH8tzgcpLiEdmHZPM0V8G2KmldJsqsuVXmb2T9l98VlPjyEOSlMGDOrj%2Fmol7zWFNCbfJWnmzObn4UlfnvKkH%2BOdNLCFQduQptRWFOO1jawDikO%2FAwg1qdHpLkkWq4Zz9Epu%2BsAIXGRS9J%2F5vkaLgcm9kLDotBbxyXfGarQ35WnUHUxJ2T%2F56XJn2Wozw%3D%3D%7Ctkp%3ABk9SR7Sv9dSdaA</t>
-  </si>
-  <si>
-    <t>Fedex 3.5kg</t>
+    <t>https://www.ebay.com/itm/287002688876?_skw=figma+Lancer+Altria&amp;itmmeta=01M3PPCANC6F89BWKQY2PE4EW7&amp;hash=item42d2b17d6c:g:z5sAAeSwrX9pOg36&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xCKVE5Omwo2QZ5431uZVFIQp74IsjHzq6rj0zZV%2BSksi%2FVWcJjFZNgDuxv4UTOYyF5rOFsROxoDrprSFFrkHqsqa3fNBDepJxYsxk%2BHESsD0cbXHW2y5oCGBN8xEjvJiCxHNd2BIqxdT3BcOluTe8Afda5yo0V6yKOE4ChZB%2FvoKVxxv2fFxCs3tiEK8pm7lex7raRCZA9EcIBKLWXKINolZZ15jjv2m%2FoxPv9ngB%2BODTSYIVeVGphu4PcufSyHWXBe8kdEYovaUqIw7HD3M%2BD5gnYkOMg6fTHeBUluwPnm%2Bw%3D%3D%7Ctkp%3ABk9SR-yqsdadaA</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>https://www.ebay.com/itm/336584550267?nordt=true&amp;orig_cvip=true&amp;rt=nc</t>
+    <t>https://www.ebay.com/sch/i.html?_nkw=Figma+Altria+Pendragon&amp;_sacat=0&amp;_from=R40&amp;_sop=15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/276056380894?_skw=Kamen+Rider+Premium&amp;itmmeta=01M3PPND0WCFZJT0DK22ZRXE2W&amp;hash=item40463e15de:g:-XYAAOSwRj5lCoX4&amp;itmprp=enc%3AAQALAAAA0GfYFPkwiKCW4ZNSs2u11xDYBdMasoFu9fkvMGSrunEbAAhv4oYhPU2G1X4RjGF7c2ocvhQOOlTvf4%2Ff%2FEZ3FpGfjTTANMPjGAMM2a4At%2B%2F%2BB4cUIii6N4c1rhSGJFhTL%2BYIj7bof%2BoNcIhDirT9IgZWBJ%2FVOrCkYIInx1IPWPn2SgbOJWG3i5rnCApza9CtfOK0YjjILuP74g6qP%2BJAQizIFIU%2BmZDtnAjrniIyZGkDYGwFPEN0ej5ln%2Byf8PrcLSud2hYlw7aGnz724D2T2A8%3D%7Ctkp%3ABk9SR9rQ1dadaA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/sch/i.html?_nkw=Kamen+Rider+Faiz+Premium+CSM&amp;_sacat=0&amp;_from=R40&amp;_trksid=m570.l1313&amp;_odkw=Figma+Altria+Pendragon&amp;_osacat=0&amp;_sop=15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/287596320225?nordt=true&amp;orig_cvip=true&amp;rt=nc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/sch/i.html?_nkw=CSM+Ghost+Driver&amp;_sacat=0&amp;_from=R40&amp;_trksid=m570.l1313&amp;_odkw=PREMIUM+DX+Magnum+Shooter+40X&amp;_osacat=0&amp;_sop=15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/sch/i.html?_nkw=PS5%20Armored%20Core%20VI%20Rubicon&amp;_sacat=0&amp;_from=R40&amp;_sop=15&amp;rt=nc&amp;_udlo=10000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/126764027482?nordt=true&amp;orig_cvip=true&amp;rt=nc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/298425371396?nordt=true&amp;orig_cvip=true&amp;rt=nc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ebay.com/sch/i.html?_nkw=ARMORED+CORE+TORCH+TORCH&amp;_sacat=0&amp;_from=R40&amp;_sop=15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fedex 7.5kg</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -499,7 +527,7 @@
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +538,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -569,12 +606,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -629,8 +669,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -970,6 +1014,7 @@
     <col min="4" max="4" width="47.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="9.625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="13.75" hidden="1" customWidth="1"/>
@@ -1116,7 +1161,7 @@
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
@@ -1127,62 +1172,62 @@
       </c>
       <c r="J2" s="7">
         <f>(G2*1.08)*0.1235</f>
-        <v>19.873620000000003</v>
+        <v>19.74024</v>
       </c>
       <c r="K2" s="7">
         <f>(G2*1.08)*0.0095</f>
-        <v>1.5287400000000002</v>
+        <v>1.5184800000000001</v>
       </c>
       <c r="L2" s="7">
         <v>0.3</v>
       </c>
       <c r="M2" s="7">
         <f>(J2+K2+L2)*0.1</f>
-        <v>2.1702360000000005</v>
+        <v>2.155872</v>
       </c>
       <c r="N2" s="7">
         <f>SUM(J2:M2)</f>
-        <v>23.872596000000001</v>
+        <v>23.714592</v>
       </c>
       <c r="O2" s="7">
         <f>G2-N2</f>
-        <v>125.127404</v>
+        <v>124.285408</v>
       </c>
       <c r="P2" s="7">
         <f>G2*0.022</f>
-        <v>3.278</v>
+        <v>3.2559999999999998</v>
       </c>
       <c r="Q2" s="7">
         <f>O2-P2</f>
-        <v>121.84940399999999</v>
+        <v>121.029408</v>
       </c>
       <c r="R2" s="7">
         <f>Q2*0.02</f>
-        <v>2.4369880799999999</v>
+        <v>2.4205881600000003</v>
       </c>
       <c r="S2" s="7">
         <f>Q2-R2</f>
-        <v>119.41241591999999</v>
+        <v>118.60881984000001</v>
       </c>
       <c r="T2" s="8">
         <f>$B$2*S2</f>
-        <v>18788.349520852797</v>
+        <v>18661.911713625603</v>
       </c>
       <c r="U2" s="7">
         <f>((G2*0.15)+4.5)/0.83</f>
-        <v>32.349397590361441</v>
+        <v>32.168674698795179</v>
       </c>
       <c r="V2" s="8">
         <f>(S2-U2)*$B$2</f>
-        <v>13698.495303985328</v>
+        <v>13600.492436517166</v>
       </c>
       <c r="W2" s="10">
         <f>IFERROR(V2-F2-I2,"")</f>
-        <v>7747.4953039853281</v>
+        <v>7649.4924365171664</v>
       </c>
       <c r="X2" s="9">
         <f>IFERROR(W2/(G2*J2),"")</f>
-        <v>2.6163634394954225</v>
+        <v>2.6182943928846392</v>
       </c>
       <c r="Y2" s="8">
         <f>IFERROR(F2*10/110,"")</f>
@@ -1190,16 +1235,18 @@
       </c>
       <c r="Z2" s="11">
         <f>IFERROR(W2+Y2,"")</f>
-        <v>7747.4953039853281</v>
+        <v>7649.4924365171664</v>
       </c>
       <c r="AA2" s="9">
         <f>IFERROR(Z2/(G2*J2),"")</f>
-        <v>2.6163634394954225</v>
-      </c>
-      <c r="AB2" s="17" t="s">
+        <v>2.6182943928846392</v>
+      </c>
+      <c r="AB2" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="AC2" s="17"/>
+      <c r="AC2" s="18" t="s">
+        <v>129</v>
+      </c>
       <c r="AD2" s="17"/>
       <c r="AE2" s="17"/>
       <c r="AF2" s="17"/>
@@ -1219,73 +1266,73 @@
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="1">
-        <v>119</v>
+        <v>346</v>
       </c>
       <c r="H3" t="s">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="I3" s="15">
         <f>IFERROR(VLOOKUP(H3,送料!$G$10:$H$28,2,FALSE),"")</f>
-        <v>5951</v>
+        <v>16789</v>
       </c>
       <c r="J3" s="7">
         <f t="shared" ref="J3:J41" si="0">(G3*1.08)*0.1235</f>
-        <v>15.87222</v>
+        <v>46.149479999999997</v>
       </c>
       <c r="K3" s="7">
         <f t="shared" ref="K3:K41" si="1">(G3*1.08)*0.0095</f>
-        <v>1.2209400000000001</v>
+        <v>3.54996</v>
       </c>
       <c r="L3" s="7">
         <v>0.3</v>
       </c>
       <c r="M3" s="7">
         <f t="shared" ref="M3:M41" si="2">(J3+K3+L3)*0.1</f>
-        <v>1.7393160000000003</v>
+        <v>4.9999439999999993</v>
       </c>
       <c r="N3" s="7">
         <f t="shared" ref="N3:N41" si="3">SUM(J3:M3)</f>
-        <v>19.132476</v>
+        <v>54.999383999999992</v>
       </c>
       <c r="O3" s="7">
         <f t="shared" ref="O3:O41" si="4">G3-N3</f>
-        <v>99.867524000000003</v>
+        <v>291.00061600000004</v>
       </c>
       <c r="P3" s="7">
         <f t="shared" ref="P3:P41" si="5">G3*0.022</f>
-        <v>2.6179999999999999</v>
+        <v>7.6119999999999992</v>
       </c>
       <c r="Q3" s="7">
         <f t="shared" ref="Q3:Q41" si="6">O3-P3</f>
-        <v>97.249524000000008</v>
+        <v>283.38861600000001</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" ref="R3:R41" si="7">Q3*0.02</f>
-        <v>1.9449904800000002</v>
+        <v>5.6677723200000001</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" ref="S3:S41" si="8">Q3-R3</f>
-        <v>95.304533520000007</v>
+        <v>277.72084368000003</v>
       </c>
       <c r="T3" s="8">
         <f t="shared" ref="T3:T41" si="9">$B$2*S3</f>
-        <v>14995.215304036801</v>
+        <v>43696.597544611206</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" ref="U3:U41" si="10">((G3*0.15)+4.5)/0.83</f>
-        <v>26.927710843373493</v>
+        <v>67.951807228915669</v>
       </c>
       <c r="V3" s="8">
         <f t="shared" ref="V3:V41" si="11">(S3-U3)*$B$2</f>
-        <v>10758.409279940417</v>
+        <v>33005.060195213613</v>
       </c>
       <c r="W3" s="10">
         <f t="shared" ref="W3:W41" si="12">IFERROR(V3-F3-I3,"")</f>
-        <v>4807.409279940417</v>
+        <v>16216.060195213613</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" ref="X3:X41" si="13">IFERROR(W3/(G3*J3),"")</f>
-        <v>2.545226648220833</v>
+        <v>1.0155526345633192</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" ref="Y3:Y41" si="14">IFERROR(F3*10/110,"")</f>
@@ -1293,16 +1340,18 @@
       </c>
       <c r="Z3" s="11">
         <f t="shared" ref="Z3:Z41" si="15">IFERROR(W3+Y3,"")</f>
-        <v>4807.409279940417</v>
+        <v>16216.060195213613</v>
       </c>
       <c r="AA3" s="9">
         <f t="shared" ref="AA3:AA41" si="16">IFERROR(Z3/(G3*J3),"")</f>
-        <v>2.545226648220833</v>
-      </c>
-      <c r="AB3" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC3" s="17"/>
+        <v>1.0155526345633192</v>
+      </c>
+      <c r="AB3" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC3" s="18" t="s">
+        <v>131</v>
+      </c>
       <c r="AD3" s="17"/>
       <c r="AE3" s="17"/>
       <c r="AF3" s="17"/>
@@ -1322,73 +1371,73 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="1">
-        <v>109</v>
+        <v>386</v>
       </c>
       <c r="H4" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I4" s="15">
         <f>IFERROR(VLOOKUP(H4,送料!$G$10:$H$28,2,FALSE),"")</f>
-        <v>5951</v>
+        <v>16789</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="0"/>
-        <v>14.538420000000002</v>
+        <v>51.484680000000004</v>
       </c>
       <c r="K4" s="7">
         <f t="shared" si="1"/>
-        <v>1.1183400000000001</v>
+        <v>3.9603600000000005</v>
       </c>
       <c r="L4" s="7">
         <v>0.3</v>
       </c>
       <c r="M4" s="7">
         <f t="shared" si="2"/>
-        <v>1.5956760000000003</v>
+        <v>5.574504000000001</v>
       </c>
       <c r="N4" s="7">
         <f t="shared" si="3"/>
-        <v>17.552436000000004</v>
+        <v>61.319544000000008</v>
       </c>
       <c r="O4" s="7">
         <f t="shared" si="4"/>
-        <v>91.447564</v>
+        <v>324.68045599999999</v>
       </c>
       <c r="P4" s="7">
         <f t="shared" si="5"/>
-        <v>2.3979999999999997</v>
+        <v>8.4919999999999991</v>
       </c>
       <c r="Q4" s="7">
         <f t="shared" si="6"/>
-        <v>89.049564000000004</v>
+        <v>316.18845599999997</v>
       </c>
       <c r="R4" s="7">
         <f t="shared" si="7"/>
-        <v>1.7809912800000001</v>
+        <v>6.3237691199999997</v>
       </c>
       <c r="S4" s="7">
         <f t="shared" si="8"/>
-        <v>87.268572720000009</v>
+        <v>309.86468687999997</v>
       </c>
       <c r="T4" s="8">
         <f t="shared" si="9"/>
-        <v>13730.837231764801</v>
+        <v>48754.109833699193</v>
       </c>
       <c r="U4" s="7">
         <f t="shared" si="10"/>
-        <v>25.120481927710841</v>
+        <v>75.180722891566262</v>
       </c>
       <c r="V4" s="8">
         <f t="shared" si="11"/>
-        <v>9778.380605258777</v>
+        <v>36925.174893940159</v>
       </c>
       <c r="W4" s="10">
         <f t="shared" si="12"/>
-        <v>3827.380605258777</v>
+        <v>20136.174893940159</v>
       </c>
       <c r="X4" s="9">
         <f t="shared" si="13"/>
-        <v>2.4152269321208348</v>
+        <v>1.0132384274684723</v>
       </c>
       <c r="Y4" s="8">
         <f t="shared" si="14"/>
@@ -1396,16 +1445,18 @@
       </c>
       <c r="Z4" s="11">
         <f t="shared" si="15"/>
-        <v>3827.380605258777</v>
+        <v>20136.174893940159</v>
       </c>
       <c r="AA4" s="9">
         <f t="shared" si="16"/>
-        <v>2.4152269321208348</v>
-      </c>
-      <c r="AB4" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC4" s="17"/>
+        <v>1.0132384274684723</v>
+      </c>
+      <c r="AB4" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC4" s="18" t="s">
+        <v>133</v>
+      </c>
       <c r="AD4" s="17"/>
       <c r="AE4" s="17"/>
       <c r="AF4" s="17"/>
@@ -1425,73 +1476,73 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="1">
-        <v>560</v>
+        <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="I5" s="15">
         <f>IFERROR(VLOOKUP(H5,送料!$G$10:$H$28,2,FALSE),"")</f>
-        <v>10966</v>
+        <v>16789</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="0"/>
-        <v>74.692800000000005</v>
+        <v>30.94416</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" si="1"/>
-        <v>5.7456000000000005</v>
+        <v>2.3803199999999998</v>
       </c>
       <c r="L5" s="7">
         <v>0.3</v>
       </c>
       <c r="M5" s="7">
         <f t="shared" si="2"/>
-        <v>8.0738400000000006</v>
+        <v>3.3624480000000001</v>
       </c>
       <c r="N5" s="7">
         <f t="shared" si="3"/>
-        <v>88.812240000000003</v>
+        <v>36.986927999999999</v>
       </c>
       <c r="O5" s="7">
         <f t="shared" si="4"/>
-        <v>471.18776000000003</v>
+        <v>195.01307199999999</v>
       </c>
       <c r="P5" s="7">
         <f t="shared" si="5"/>
-        <v>12.319999999999999</v>
+        <v>5.1040000000000001</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" si="6"/>
-        <v>458.86776000000003</v>
+        <v>189.90907199999998</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" si="7"/>
-        <v>9.1773552000000009</v>
+        <v>3.7981814399999996</v>
       </c>
       <c r="S5" s="7">
         <f t="shared" si="8"/>
-        <v>449.69040480000001</v>
+        <v>186.11089055999997</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" si="9"/>
-        <v>70754.288291232006</v>
+        <v>29282.687520710395</v>
       </c>
       <c r="U5" s="7">
         <f t="shared" si="10"/>
-        <v>106.62650602409639</v>
+        <v>47.349397590361441</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="11"/>
-        <v>53977.67383340068</v>
+        <v>21832.733303842928</v>
       </c>
       <c r="W5" s="10">
         <f t="shared" si="12"/>
-        <v>43011.67383340068</v>
+        <v>5043.7333038429279</v>
       </c>
       <c r="X5" s="9">
         <f t="shared" si="13"/>
-        <v>1.0282993865109746</v>
+        <v>0.70256325451857982</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="14"/>
@@ -1499,16 +1550,18 @@
       </c>
       <c r="Z5" s="11">
         <f t="shared" si="15"/>
-        <v>43011.67383340068</v>
+        <v>5043.7333038429279</v>
       </c>
       <c r="AA5" s="9">
         <f t="shared" si="16"/>
-        <v>1.0282993865109746</v>
-      </c>
-      <c r="AB5" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC5" s="17"/>
+        <v>0.70256325451857982</v>
+      </c>
+      <c r="AB5" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="AC5" s="18" t="s">
+        <v>134</v>
+      </c>
       <c r="AD5" s="17"/>
       <c r="AE5" s="17"/>
       <c r="AF5" s="17"/>
@@ -1527,84 +1580,93 @@
         <v>5</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="I6" s="15" t="str">
+      <c r="G6" s="1">
+        <v>1030</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15">
         <f>IFERROR(VLOOKUP(H6,送料!$G$10:$H$28,2,FALSE),"")</f>
-        <v/>
+        <v>5951</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>137.38140000000001</v>
       </c>
       <c r="K6" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10.5678</v>
       </c>
       <c r="L6" s="7">
         <v>0.3</v>
       </c>
       <c r="M6" s="7">
         <f t="shared" si="2"/>
-        <v>0.03</v>
+        <v>14.824920000000004</v>
       </c>
       <c r="N6" s="7">
         <f t="shared" si="3"/>
-        <v>0.32999999999999996</v>
+        <v>163.07412000000002</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" si="4"/>
-        <v>-0.32999999999999996</v>
+        <v>866.92588000000001</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>22.66</v>
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="6"/>
-        <v>-0.32999999999999996</v>
+        <v>844.26588000000004</v>
       </c>
       <c r="R6" s="7">
         <f t="shared" si="7"/>
-        <v>-6.5999999999999991E-3</v>
+        <v>16.8853176</v>
       </c>
       <c r="S6" s="7">
         <f t="shared" si="8"/>
-        <v>-0.32339999999999997</v>
+        <v>827.38056240000003</v>
       </c>
       <c r="T6" s="8">
         <f t="shared" si="9"/>
-        <v>-50.883755999999998</v>
+        <v>130180.05768801601</v>
       </c>
       <c r="U6" s="7">
         <f t="shared" si="10"/>
-        <v>5.4216867469879517</v>
+        <v>191.56626506024097</v>
       </c>
       <c r="V6" s="8">
         <f t="shared" si="11"/>
-        <v>-903.93194877108442</v>
-      </c>
-      <c r="W6" s="10" t="str">
+        <v>100039.02154343769</v>
+      </c>
+      <c r="W6" s="10">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="str">
+        <v>94088.021543437688</v>
+      </c>
+      <c r="X6" s="9">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0.66491965965911615</v>
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="11" t="str">
+      <c r="Z6" s="11">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="str">
+        <v>94088.021543437688</v>
+      </c>
+      <c r="AA6" s="9">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
+        <v>0.66491965965911615</v>
+      </c>
+      <c r="AB6" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC6" s="18" t="s">
+        <v>137</v>
+      </c>
       <c r="AD6" s="17"/>
       <c r="AE6" s="17"/>
       <c r="AF6" s="17"/>
@@ -4860,6 +4922,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="AB2" r:id="rId1" display="https://www.ebay.com/itm/287002688876?_skw=figma+Lancer+Altria&amp;itmmeta=01M3PPCANC6F89BWKQY2PE4EW7&amp;hash=item42d2b17d6c:g:z5sAAeSwrX9pOg36&amp;itmprp=enc%3AAQALAAAA8GfYFPkwiKCW4ZNSs2u11xCKVE5Omwo2QZ5431uZVFIQp74IsjHzq6rj0zZV%2BSksi%2FVWcJjFZNgDuxv4UTOYyF5rOFsROxoDrprSFFrkHqsqa3fNBDepJxYsxk%2BHESsD0cbXHW2y5oCGBN8xEjvJiCxHNd2BIqxdT3BcOluTe8Afda5yo0V6yKOE4ChZB%2FvoKVxxv2fFxCs3tiEK8pm7lex7raRCZA9EcIBKLWXKINolZZ15jjv2m%2FoxPv9ngB%2BODTSYIVeVGphu4PcufSyHWXBe8kdEYovaUqIw7HD3M%2BD5gnYkOMg6fTHeBUluwPnm%2Bw%3D%3D%7Ctkp%3ABk9SR-yqsdadaA" xr:uid="{FFD3AEF5-04ED-486F-BB80-5982F8F0C05B}"/>
+    <hyperlink ref="AC2" r:id="rId2" xr:uid="{CC3A7FD5-254C-4A17-A968-39B25FE67977}"/>
+    <hyperlink ref="AB3" r:id="rId3" display="https://www.ebay.com/itm/276056380894?_skw=Kamen+Rider+Premium&amp;itmmeta=01M3PPND0WCFZJT0DK22ZRXE2W&amp;hash=item40463e15de:g:-XYAAOSwRj5lCoX4&amp;itmprp=enc%3AAQALAAAA0GfYFPkwiKCW4ZNSs2u11xDYBdMasoFu9fkvMGSrunEbAAhv4oYhPU2G1X4RjGF7c2ocvhQOOlTvf4%2Ff%2FEZ3FpGfjTTANMPjGAMM2a4At%2B%2F%2BB4cUIii6N4c1rhSGJFhTL%2BYIj7bof%2BoNcIhDirT9IgZWBJ%2FVOrCkYIInx1IPWPn2SgbOJWG3i5rnCApza9CtfOK0YjjILuP74g6qP%2BJAQizIFIU%2BmZDtnAjrniIyZGkDYGwFPEN0ej5ln%2Byf8PrcLSud2hYlw7aGnz724D2T2A8%3D%7Ctkp%3ABk9SR9rQ1dadaA" xr:uid="{CF8B1A64-5FE9-4421-80D3-A2D9F552E956}"/>
+    <hyperlink ref="AC3" r:id="rId4" xr:uid="{8CF0B208-BE63-4CD6-ABB8-09E473AED5D6}"/>
+    <hyperlink ref="AB4" r:id="rId5" xr:uid="{68558723-A736-4848-AB95-41D60EA8B429}"/>
+    <hyperlink ref="AC4" r:id="rId6" xr:uid="{0D2E2F92-276C-4203-A1E7-6A4078B5C54C}"/>
+    <hyperlink ref="AC5" r:id="rId7" xr:uid="{C0F0EBCD-4AA4-4C53-84C0-597FD47067A7}"/>
+    <hyperlink ref="AB5" r:id="rId8" xr:uid="{2EF9BD89-E444-48CA-A22F-44B01A85DFF4}"/>
+    <hyperlink ref="AB6" r:id="rId9" xr:uid="{3731AD34-C24A-48DA-929D-3F239707F3E1}"/>
+    <hyperlink ref="AC6" r:id="rId10" xr:uid="{2E67BC9E-409C-492E-9149-5D05E04BD191}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
